--- a/data/prediction_logs.xlsx
+++ b/data/prediction_logs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vardhaman.patankar\Documents\XRayDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{462141BA-3616-4A4C-8F39-63C070D0E01D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D186E553-2C53-4C94-8A48-B88F622C9A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{94C11F78-FB75-4283-B718-B16A1EE8128F}"/>
   </bookViews>
